--- a/electron/data/summary_portfolio1.xlsx
+++ b/electron/data/summary_portfolio1.xlsx
@@ -475,16 +475,16 @@
         <v>384.2120704545454</v>
       </c>
       <c r="I2">
-        <v>449.88</v>
+        <v>444</v>
       </c>
       <c r="J2">
-        <v>-0.64</v>
+        <v>-6.52</v>
       </c>
       <c r="K2" t="str">
-        <v>(-0.14%)</v>
+        <v>(-1.45%)</v>
       </c>
       <c r="L2">
-        <v>17.09158420446436</v>
+        <v>15.561179396243835</v>
       </c>
       <c r="M2">
         <v>95.90637295493026</v>
@@ -522,16 +522,16 @@
         <v>18.0395</v>
       </c>
       <c r="I3">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="J3">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="K3" t="str">
-        <v>(0.98%)</v>
+        <v>(1.05%)</v>
       </c>
       <c r="L3">
-        <v>76.7233016436154</v>
+        <v>76.83416946145957</v>
       </c>
       <c r="M3">
         <v>4.0936270450697405</v>

--- a/electron/data/summary_portfolio1.xlsx
+++ b/electron/data/summary_portfolio1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:O3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,9 +445,6 @@
       <c r="O1" t="str">
         <v>dividendIncome</v>
       </c>
-      <c r="P1" t="str">
-        <v>rawJson</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -475,16 +472,16 @@
         <v>384.2120704545454</v>
       </c>
       <c r="I2">
-        <v>444</v>
+        <v>444.8</v>
       </c>
       <c r="J2">
-        <v>-6.52</v>
+        <v>-5.72</v>
       </c>
       <c r="K2" t="str">
-        <v>(-1.45%)</v>
+        <v>(-1.27%)</v>
       </c>
       <c r="L2">
-        <v>15.561179396243835</v>
+        <v>15.769397737498334</v>
       </c>
       <c r="M2">
         <v>95.90637295493026</v>
@@ -545,7 +542,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/electron/data/summary_portfolio1.xlsx
+++ b/electron/data/summary_portfolio1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -463,13 +463,13 @@
         <v>COMMERCIAL BANKS</v>
       </c>
       <c r="F2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>42263.32775</v>
+        <v>40069.5</v>
       </c>
       <c r="H2">
-        <v>384.2120704545454</v>
+        <v>400.695</v>
       </c>
       <c r="I2">
         <v>444.8</v>
@@ -481,10 +481,10 @@
         <v>(-1.27%)</v>
       </c>
       <c r="L2">
-        <v>15.769397737498334</v>
+        <v>11.007125120103824</v>
       </c>
       <c r="M2">
-        <v>95.90637295493026</v>
+        <v>19.511868508719765</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -510,13 +510,13 @@
         <v>REAL ESTATE INVESTMENT TRUST</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G3">
-        <v>1803.95</v>
+        <v>25048.125</v>
       </c>
       <c r="H3">
-        <v>18.0395</v>
+        <v>25.048125</v>
       </c>
       <c r="I3">
         <v>31.9</v>
@@ -528,21 +528,68 @@
         <v>(1.05%)</v>
       </c>
       <c r="L3">
-        <v>76.83416946145957</v>
+        <v>27.354841929286124</v>
       </c>
       <c r="M3">
-        <v>4.0936270450697405</v>
+        <v>12.197200399056046</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SAZEW</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Equity</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Sazgar Engineering Works Limited</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v>AUTOMOBILE ASSEMBLER</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>140242</v>
+      </c>
+      <c r="H4">
+        <v>1402.42</v>
+      </c>
+      <c r="I4" t="str">
+        <v>1,912.88</v>
+      </c>
+      <c r="J4">
+        <v>-40.01</v>
+      </c>
+      <c r="K4" t="str">
+        <v>(-2.05%)</v>
+      </c>
+      <c r="L4">
+        <v>36.39851114502075</v>
+      </c>
+      <c r="M4">
+        <v>68.2909310922242</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/electron/data/summary_portfolio1.xlsx
+++ b/electron/data/summary_portfolio1.xlsx
@@ -472,16 +472,16 @@
         <v>400.695</v>
       </c>
       <c r="I2">
-        <v>444.8</v>
+        <v>444.99</v>
       </c>
       <c r="J2">
-        <v>-5.72</v>
+        <v>2.6</v>
       </c>
       <c r="K2" t="str">
-        <v>(-1.27%)</v>
+        <v>(0.59%)</v>
       </c>
       <c r="L2">
-        <v>11.007125120103824</v>
+        <v>11.05454273200315</v>
       </c>
       <c r="M2">
         <v>19.511868508719765</v>
@@ -519,16 +519,16 @@
         <v>25.048125</v>
       </c>
       <c r="I3">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="J3">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="K3" t="str">
-        <v>(1.05%)</v>
+        <v>(0.57%)</v>
       </c>
       <c r="L3">
-        <v>27.354841929286124</v>
+        <v>27.674227112807852</v>
       </c>
       <c r="M3">
         <v>12.197200399056046</v>
@@ -566,16 +566,16 @@
         <v>1402.42</v>
       </c>
       <c r="I4" t="str">
-        <v>1,912.88</v>
+        <v>1,939.00</v>
       </c>
       <c r="J4">
-        <v>-40.01</v>
+        <v>16.96</v>
       </c>
       <c r="K4" t="str">
-        <v>(-2.05%)</v>
+        <v>(0.88%)</v>
       </c>
       <c r="L4">
-        <v>36.39851114502075</v>
+        <v>38.2610059753854</v>
       </c>
       <c r="M4">
         <v>68.2909310922242</v>
